--- a/KatalonData/RADTestData/FEINandFEINSSNlessThan9Error.xlsx
+++ b/KatalonData/RADTestData/FEINandFEINSSNlessThan9Error.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="137">
   <si>
     <t>Result</t>
   </si>
@@ -294,12 +294,166 @@
   </si>
   <si>
     <t>Sun Aug 02 19:17:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:19:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:20:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:21:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:23:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:24:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:26:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:26:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:27:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:27:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:28:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:28:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:29:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:29:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:30:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:31:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:31:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:32:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:32:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:33:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:33:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:34:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:34:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:35:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:36:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:36:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:37:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:37:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:38:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:38:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:39:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:39:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:39:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:40:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:41:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:41:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:42:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:42:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:43:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:43:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:44:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:44:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:45:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:45:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:45:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:46:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:46:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:47:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:47:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:48:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:48:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:49:03 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -666,13 +820,13 @@
   <dimension ref="A1:F55"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="26.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="17.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="49.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="40.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="17.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.53125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="17.53125" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="49.19921875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="40.796875" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="1" width="17.73046875" collapsed="true"/>
+    <col min="7" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -700,7 +854,7 @@
         <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
@@ -717,7 +871,7 @@
         <v>21</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>4</v>
@@ -734,7 +888,7 @@
         <v>21</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -751,7 +905,7 @@
         <v>21</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>
@@ -771,7 +925,7 @@
         <v>21</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>4</v>
@@ -791,7 +945,7 @@
         <v>21</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>4</v>
@@ -808,7 +962,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>4</v>
@@ -825,7 +979,7 @@
         <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>4</v>
@@ -842,7 +996,7 @@
         <v>21</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>4</v>
@@ -859,7 +1013,7 @@
         <v>21</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>4</v>
@@ -879,7 +1033,7 @@
         <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>4</v>
@@ -899,7 +1053,7 @@
         <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>4</v>
@@ -916,7 +1070,7 @@
         <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>4</v>
@@ -933,7 +1087,7 @@
         <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>4</v>
@@ -953,7 +1107,7 @@
         <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>4</v>
@@ -973,7 +1127,7 @@
         <v>21</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>4</v>
@@ -993,7 +1147,7 @@
         <v>21</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>4</v>
@@ -1013,7 +1167,7 @@
         <v>21</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>4</v>
@@ -1030,7 +1184,7 @@
         <v>21</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>53</v>
+        <v>104</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>4</v>
@@ -1047,7 +1201,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>4</v>
@@ -1067,7 +1221,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>55</v>
+        <v>106</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>4</v>
@@ -1087,7 +1241,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>4</v>
@@ -1107,7 +1261,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>4</v>
@@ -1127,7 +1281,7 @@
         <v>21</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>4</v>
@@ -1144,7 +1298,7 @@
         <v>21</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>4</v>
@@ -1164,7 +1318,7 @@
         <v>21</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>4</v>
@@ -1184,7 +1338,7 @@
         <v>21</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>4</v>
@@ -1204,7 +1358,7 @@
         <v>21</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>62</v>
+        <v>113</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>4</v>
@@ -1224,7 +1378,7 @@
         <v>21</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>4</v>
@@ -1241,7 +1395,7 @@
         <v>21</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>64</v>
+        <v>115</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>4</v>
@@ -1258,7 +1412,7 @@
         <v>21</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>65</v>
+        <v>116</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>4</v>
@@ -1275,7 +1429,7 @@
         <v>21</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>4</v>
@@ -1295,7 +1449,7 @@
         <v>21</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>4</v>
@@ -1312,7 +1466,7 @@
         <v>21</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>4</v>
@@ -1346,7 +1500,7 @@
         <v>21</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>4</v>
@@ -1363,7 +1517,7 @@
         <v>21</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>70</v>
+        <v>121</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>4</v>
@@ -1380,7 +1534,7 @@
         <v>21</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>4</v>
@@ -1397,7 +1551,7 @@
         <v>21</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>4</v>
@@ -1414,7 +1568,7 @@
         <v>21</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>4</v>
@@ -1431,7 +1585,7 @@
         <v>21</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>4</v>
@@ -1448,7 +1602,7 @@
         <v>21</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>4</v>
@@ -1465,7 +1619,7 @@
         <v>21</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>4</v>
@@ -1482,7 +1636,7 @@
         <v>21</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>4</v>
@@ -1502,7 +1656,7 @@
         <v>21</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>4</v>
@@ -1519,7 +1673,7 @@
         <v>21</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>79</v>
+        <v>130</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>4</v>
@@ -1539,7 +1693,7 @@
         <v>21</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>4</v>
@@ -1556,7 +1710,7 @@
         <v>21</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>4</v>
@@ -1573,7 +1727,7 @@
         <v>21</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>82</v>
+        <v>133</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>4</v>
@@ -1617,8 +1771,8 @@
       <c r="A53" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B53" t="s">
-        <v>85</v>
+      <c r="B53" t="s" s="1">
+        <v>134</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>4</v>
@@ -1638,7 +1792,7 @@
         <v>21</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>4</v>
@@ -1655,7 +1809,7 @@
         <v>21</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>4</v>

--- a/KatalonData/RADTestData/FEINandFEINSSNlessThan9Error.xlsx
+++ b/KatalonData/RADTestData/FEINandFEINSSNlessThan9Error.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="137">
   <si>
     <t>Result</t>
   </si>
@@ -294,12 +294,166 @@
   </si>
   <si>
     <t>Sun Aug 02 19:17:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:51:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:51:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:52:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:52:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:52:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:52:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:52:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:53:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:53:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:53:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:53:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:53:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:53:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:54:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:54:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:54:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:54:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:54:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:54:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:54:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:55:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:55:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:55:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:55:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:55:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:55:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:56:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:56:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:56:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:56:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:56:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:56:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:57:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:57:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:57:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:57:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:57:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:57:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:58:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:58:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:58:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:58:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:58:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:58:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:59:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:59:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:59:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:59:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:59:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 21:59:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:00:04 EDT 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -666,13 +820,13 @@
   <dimension ref="A1:F55"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="26.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="17.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="49.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="40.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="17.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.53125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="17.53125" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="49.19921875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="40.796875" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="1" width="17.73046875" collapsed="true"/>
+    <col min="7" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -700,7 +854,7 @@
         <v>21</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
@@ -717,7 +871,7 @@
         <v>21</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>4</v>
@@ -734,7 +888,7 @@
         <v>21</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -751,7 +905,7 @@
         <v>21</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>
@@ -771,7 +925,7 @@
         <v>21</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>4</v>
@@ -791,7 +945,7 @@
         <v>21</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>4</v>
@@ -808,7 +962,7 @@
         <v>21</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>4</v>
@@ -825,7 +979,7 @@
         <v>21</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>4</v>
@@ -842,7 +996,7 @@
         <v>21</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>4</v>
@@ -859,7 +1013,7 @@
         <v>21</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>4</v>
@@ -879,7 +1033,7 @@
         <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>4</v>
@@ -899,7 +1053,7 @@
         <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>4</v>
@@ -916,7 +1070,7 @@
         <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>4</v>
@@ -933,7 +1087,7 @@
         <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>4</v>
@@ -953,7 +1107,7 @@
         <v>21</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>4</v>
@@ -973,7 +1127,7 @@
         <v>21</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>4</v>
@@ -993,7 +1147,7 @@
         <v>21</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>4</v>
@@ -1013,7 +1167,7 @@
         <v>21</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>4</v>
@@ -1030,7 +1184,7 @@
         <v>21</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>53</v>
+        <v>104</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>4</v>
@@ -1047,7 +1201,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>4</v>
@@ -1067,7 +1221,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>55</v>
+        <v>106</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>4</v>
@@ -1087,7 +1241,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>4</v>
@@ -1107,7 +1261,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>4</v>
@@ -1127,7 +1281,7 @@
         <v>21</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>4</v>
@@ -1144,7 +1298,7 @@
         <v>21</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>4</v>
@@ -1164,7 +1318,7 @@
         <v>21</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>4</v>
@@ -1184,7 +1338,7 @@
         <v>21</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>4</v>
@@ -1204,7 +1358,7 @@
         <v>21</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>62</v>
+        <v>113</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>4</v>
@@ -1224,7 +1378,7 @@
         <v>21</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>4</v>
@@ -1241,7 +1395,7 @@
         <v>21</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>64</v>
+        <v>115</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>4</v>
@@ -1258,7 +1412,7 @@
         <v>21</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>65</v>
+        <v>116</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>4</v>
@@ -1275,7 +1429,7 @@
         <v>21</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>4</v>
@@ -1295,7 +1449,7 @@
         <v>21</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>4</v>
@@ -1312,7 +1466,7 @@
         <v>21</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>4</v>
@@ -1346,7 +1500,7 @@
         <v>21</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>4</v>
@@ -1363,7 +1517,7 @@
         <v>21</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>70</v>
+        <v>121</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>4</v>
@@ -1380,7 +1534,7 @@
         <v>21</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>4</v>
@@ -1397,7 +1551,7 @@
         <v>21</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>4</v>
@@ -1414,7 +1568,7 @@
         <v>21</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>4</v>
@@ -1431,7 +1585,7 @@
         <v>21</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>4</v>
@@ -1448,7 +1602,7 @@
         <v>21</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>4</v>
@@ -1465,7 +1619,7 @@
         <v>21</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>4</v>
@@ -1482,7 +1636,7 @@
         <v>21</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>4</v>
@@ -1502,7 +1656,7 @@
         <v>21</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>4</v>
@@ -1519,7 +1673,7 @@
         <v>21</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>79</v>
+        <v>130</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>4</v>
@@ -1539,7 +1693,7 @@
         <v>21</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>4</v>
@@ -1556,7 +1710,7 @@
         <v>21</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>4</v>
@@ -1573,7 +1727,7 @@
         <v>21</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>82</v>
+        <v>133</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>4</v>
@@ -1617,8 +1771,8 @@
       <c r="A53" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B53" t="s">
-        <v>85</v>
+      <c r="B53" t="s" s="1">
+        <v>134</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>4</v>
@@ -1638,7 +1792,7 @@
         <v>21</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>4</v>
@@ -1655,7 +1809,7 @@
         <v>21</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>4</v>
